--- a/docs/database/数据字典与数据项清单.xlsx
+++ b/docs/database/数据字典与数据项清单.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 数据项清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 数据表清单" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 字段字典" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 码表与枚举" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 索引与约束" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 存储规划" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 数据流转" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 容量汇总" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="00 说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01 数据项清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02 数据表清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03 字段字典" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04 码表与枚举" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05 索引与约束" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06 存储规划" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07 数据流转" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08 容量汇总" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 数据项清单'!$A$3:$K$261</definedName>
